--- a/data/trans_dic/IP04D$colectiva-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,89</t>
+          <t>0,48; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,62</t>
+          <t>1,13; 6,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 15,79</t>
+          <t>6,8; 15,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,64</t>
+          <t>0,4; 3,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,24</t>
+          <t>0,51; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,15</t>
+          <t>2,09; 7,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,34</t>
+          <t>0,67; 3,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,22</t>
+          <t>1,04; 4,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,44</t>
+          <t>4,96; 9,97</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,73</t>
+          <t>2,58; 7,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,19</t>
+          <t>0,93; 4,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,48</t>
+          <t>4,85; 11,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,53</t>
+          <t>1,77; 5,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,91</t>
+          <t>0,6; 3,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,25</t>
+          <t>4,74; 9,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,77</t>
+          <t>2,65; 5,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,4</t>
+          <t>1,0; 3,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,55</t>
+          <t>5,45; 9,67</t>
         </is>
       </c>
     </row>
@@ -900,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,23</t>
+          <t>0,84; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,68</t>
+          <t>2,63; 8,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,76</t>
+          <t>0,4; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,83</t>
+          <t>0,81; 5,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,06</t>
+          <t>2,9; 9,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,65</t>
+          <t>0,56; 2,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,98</t>
+          <t>1,21; 4,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,92</t>
+          <t>3,51; 7,79</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,24</t>
+          <t>2,99; 7,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,82</t>
+          <t>3,45; 9,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 12,42</t>
+          <t>5,72; 12,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,55</t>
+          <t>2,17; 7,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,83</t>
+          <t>5,45; 12,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,09</t>
+          <t>7,0; 15,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,96</t>
+          <t>3,01; 6,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,17</t>
+          <t>5,09; 9,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,58</t>
+          <t>7,16; 12,72</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,79</t>
+          <t>2,54; 4,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,7</t>
+          <t>2,48; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,87</t>
+          <t>6,24; 9,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,98</t>
+          <t>2,0; 3,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,84</t>
+          <t>2,62; 4,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,64</t>
+          <t>5,56; 8,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,02</t>
+          <t>2,46; 3,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,33</t>
+          <t>2,79; 4,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,48</t>
+          <t>6,17; 8,6</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2874</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12596</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18143</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>669; 6895</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1502; 9018</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7980; 18077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>619; 5583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>757; 6169</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2932; 9938</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1978; 10046</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2932; 11274</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12774; 25686</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9888</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4484</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14952</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17735</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17294</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8170</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>32687</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5293; 15376</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1908; 8943</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9191; 22289</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3971; 12725</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1343; 7731</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12062; 25349</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11381; 24390</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4282; 13583</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>24210; 42913</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2518</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10069</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20478</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1314; 7805</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5015; 16878</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>667; 6677</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1342; 8456</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5367; 17386</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1803; 8397</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3910; 13066</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13183; 29262</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10578</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11651</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14168</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8952</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16624</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19412</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19530</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>28275</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>33580</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6260; 16702</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7080; 18906</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9603; 21234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4526; 16280</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11019; 24632</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12620; 28826</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12584; 28594</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>20764; 38556</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24929; 44287</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24802</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24276</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52125</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52763</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>50484</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>104888</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>17982; 34398</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17392; 33867</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>41484; 64809</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15008; 30035</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19382; 35710</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>42303; 65963</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>35902; 57350</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>40111; 64109</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>87935; 122650</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$colectiva-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,98</t>
+          <t>0,49; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,79</t>
+          <t>1,1; 6,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 15,41</t>
+          <t>7,37; 15,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,61</t>
+          <t>0,41; 3,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,17</t>
+          <t>0,51; 4,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,08</t>
+          <t>2,07; 7,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,43</t>
+          <t>0,73; 3,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,01</t>
+          <t>1,09; 4,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,97</t>
+          <t>4,92; 9,83</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,5</t>
+          <t>2,77; 7,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,34</t>
+          <t>0,91; 4,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,76</t>
+          <t>4,88; 11,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,69</t>
+          <t>1,77; 5,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,46</t>
+          <t>0,59; 3,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,97</t>
+          <t>4,77; 10,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,69</t>
+          <t>2,75; 5,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,16</t>
+          <t>1,11; 3,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 9,67</t>
+          <t>5,46; 9,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,0</t>
+          <t>1,17; 4,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,86</t>
+          <t>2,92; 9,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,04</t>
+          <t>0,4; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,1</t>
+          <t>0,84; 4,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,38</t>
+          <t>3,07; 9,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,62</t>
+          <t>0,49; 2,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,06</t>
+          <t>1,2; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,79</t>
+          <t>3,78; 8,24</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,97</t>
+          <t>2,74; 7,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,21</t>
+          <t>3,4; 8,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 12,64</t>
+          <t>5,41; 12,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,81</t>
+          <t>2,22; 7,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 12,17</t>
+          <t>5,33; 11,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 15,99</t>
+          <t>7,19; 14,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,84</t>
+          <t>3,06; 6,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,46</t>
+          <t>4,87; 9,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,72</t>
+          <t>6,92; 12,46</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,86</t>
+          <t>2,46; 4,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,84</t>
+          <t>2,57; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,74</t>
+          <t>6,17; 9,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,99</t>
+          <t>1,9; 3,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,83</t>
+          <t>2,5; 4,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,68</t>
+          <t>5,4; 8,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,93</t>
+          <t>2,37; 3,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,45</t>
+          <t>2,78; 4,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,6</t>
+          <t>6,31; 8,62</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>669; 6895</t>
+          <t>680; 7321</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1502; 9018</t>
+          <t>1458; 8759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7980; 18077</t>
+          <t>8638; 18721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>619; 5583</t>
+          <t>631; 5845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>757; 6169</t>
+          <t>754; 6184</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2932; 9938</t>
+          <t>2906; 10704</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1978; 10046</t>
+          <t>2131; 9842</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2932; 11274</t>
+          <t>3058; 11975</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12774; 25686</t>
+          <t>12669; 25329</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5293; 15376</t>
+          <t>5684; 16050</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1908; 8943</t>
+          <t>1882; 9095</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9191; 22289</t>
+          <t>9257; 21539</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3971; 12725</t>
+          <t>3961; 12852</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1343; 7731</t>
+          <t>1323; 8020</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12062; 25349</t>
+          <t>12126; 25609</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11381; 24390</t>
+          <t>11814; 24813</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4282; 13583</t>
+          <t>4760; 14500</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24210; 42913</t>
+          <t>24247; 41661</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1314; 7805</t>
+          <t>1831; 7409</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5015; 16878</t>
+          <t>5562; 17172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667; 6677</t>
+          <t>666; 6410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1342; 8456</t>
+          <t>1401; 8051</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5367; 17386</t>
+          <t>5690; 17607</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1803; 8397</t>
+          <t>1580; 8183</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3910; 13066</t>
+          <t>3865; 12591</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13183; 29262</t>
+          <t>14197; 30973</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6260; 16702</t>
+          <t>5734; 16287</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7080; 18906</t>
+          <t>6977; 18037</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9603; 21234</t>
+          <t>9082; 20740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4526; 16280</t>
+          <t>4628; 16070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11019; 24632</t>
+          <t>10785; 23713</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12620; 28826</t>
+          <t>12961; 27012</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12584; 28594</t>
+          <t>12806; 28704</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20764; 38556</t>
+          <t>19856; 37427</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24929; 44287</t>
+          <t>24096; 43392</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17982; 34398</t>
+          <t>17440; 32935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17392; 33867</t>
+          <t>18023; 34452</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41484; 64809</t>
+          <t>41031; 64200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15008; 30035</t>
+          <t>14277; 29047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19382; 35710</t>
+          <t>18514; 35369</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42303; 65963</t>
+          <t>41076; 65804</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35902; 57350</t>
+          <t>34629; 58113</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40111; 64109</t>
+          <t>40100; 63666</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87935; 122650</t>
+          <t>89985; 122939</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$colectiva-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,29</t>
+          <t>0,41; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,59</t>
+          <t>0,51; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 15,96</t>
+          <t>2,01; 6,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,78</t>
+          <t>0,49; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,18</t>
+          <t>1,11; 6,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,62</t>
+          <t>6,78; 15,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,36</t>
+          <t>0,67; 3,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,26</t>
+          <t>1,03; 4,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,83</t>
+          <t>4,97; 9,64</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,83</t>
+          <t>1,77; 5,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,42</t>
+          <t>0,64; 3,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,37</t>
+          <t>4,2; 9,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,74</t>
+          <t>2,88; 7,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,59</t>
+          <t>0,92; 4,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,07</t>
+          <t>5,13; 12,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,79</t>
+          <t>2,82; 5,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,37</t>
+          <t>1,11; 3,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,39</t>
+          <t>5,29; 9,46</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,41; 3,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,75</t>
+          <t>0,87; 4,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,02</t>
+          <t>2,91; 9,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,88</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,85</t>
+          <t>0,86; 5,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,5</t>
+          <t>4,07; 12,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,55</t>
+          <t>0,48; 2,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,91</t>
+          <t>1,25; 3,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,24</t>
+          <t>4,2; 9,02</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,77</t>
+          <t>2,27; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,78</t>
+          <t>5,35; 11,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,35</t>
+          <t>7,28; 15,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,71</t>
+          <t>2,81; 8,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,72</t>
+          <t>3,28; 8,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 14,98</t>
+          <t>5,42; 12,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,87</t>
+          <t>3,18; 6,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,18</t>
+          <t>4,94; 9,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,46</t>
+          <t>7,14; 12,59</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,65</t>
+          <t>1,89; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,92</t>
+          <t>2,58; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,65</t>
+          <t>5,36; 8,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,86</t>
+          <t>2,57; 4,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,78</t>
+          <t>2,46; 4,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,65</t>
+          <t>6,82; 10,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,98</t>
+          <t>2,46; 4,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,42</t>
+          <t>2,7; 4,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,62</t>
+          <t>6,42; 8,68</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2874</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>4314</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12596</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2096</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2326</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>17520</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>680; 7321</t>
+          <t>629; 5629</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1458; 8759</t>
+          <t>761; 6278</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8638; 18721</t>
+          <t>2529; 8803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>631; 5845</t>
+          <t>683; 6765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>754; 6184</t>
+          <t>1472; 8803</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2906; 10704</t>
+          <t>8208; 18881</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2131; 9842</t>
+          <t>1973; 9792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3058; 11975</t>
+          <t>2906; 11851</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12669; 25329</t>
+          <t>12274; 23815</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15177</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>9888</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4484</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14952</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7406</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3686</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32687</t>
+          <t>30282</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5684; 16050</t>
+          <t>3962; 12374</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1882; 9095</t>
+          <t>1440; 8755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9257; 21539</t>
+          <t>9943; 22369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3961; 12852</t>
+          <t>5912; 15840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1323; 8020</t>
+          <t>1894; 8626</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12126; 25609</t>
+          <t>9408; 22195</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11814; 24813</t>
+          <t>12078; 24732</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4760; 14500</t>
+          <t>4768; 14622</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24247; 41661</t>
+          <t>22198; 39718</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2518</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9529</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1462</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>3827</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10409</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2518</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>20506</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5556</t>
+          <t>670; 6223</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1831; 7409</t>
+          <t>1437; 8007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5562; 17172</t>
+          <t>4903; 15989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666; 6410</t>
+          <t>0; 5222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1401; 8051</t>
+          <t>1345; 8162</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5690; 17607</t>
+          <t>6387; 18937</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1580; 8183</t>
+          <t>1550; 8507</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3865; 12591</t>
+          <t>4010; 12796</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14197; 30973</t>
+          <t>13661; 29365</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8952</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16624</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17991</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>10578</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>11651</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14168</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8952</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16624</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>32167</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5734; 16287</t>
+          <t>4741; 15730</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6977; 18037</t>
+          <t>10825; 23940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9082; 20740</t>
+          <t>12269; 25402</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4628; 16070</t>
+          <t>5895; 17268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10785; 23713</t>
+          <t>6727; 18118</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12961; 27012</t>
+          <t>9067; 20594</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12806; 28704</t>
+          <t>13275; 29081</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19856; 37427</t>
+          <t>20128; 37399</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24096; 43392</t>
+          <t>23954; 42256</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17440; 32935</t>
+          <t>14210; 29957</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18023; 34452</t>
+          <t>19093; 35833</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41031; 64200</t>
+          <t>37489; 59236</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14277; 29047</t>
+          <t>18213; 33912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18514; 35369</t>
+          <t>17194; 32882</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41076; 65804</t>
+          <t>42864; 66630</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34629; 58113</t>
+          <t>35876; 58667</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40100; 63666</t>
+          <t>38814; 62323</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89985; 122939</t>
+          <t>85194; 115246</t>
         </is>
       </c>
     </row>
